--- a/files/data/NomNavire.xlsx
+++ b/files/data/NomNavire.xlsx
@@ -1,45 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexandreETIENNE\Downloads\pERSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/054f950197fbca64/Documents/Jeu/PavillonNoirLogiciel/LogicielPNGaming/files/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21EFF6A-C0BA-4977-AFEB-3DB6BA899170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A21EFF6A-C0BA-4977-AFEB-3DB6BA899170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BAA370B-A538-4754-98CD-CC1B1FFDC072}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{26216F7E-DD65-4221-AEB8-E7BDD12690AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26216F7E-DD65-4221-AEB8-E7BDD12690AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$B$1254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$B$1366</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1215">
   <si>
     <t>Nom</t>
   </si>
@@ -3681,6 +3670,9 @@
   </si>
   <si>
     <t>PU</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -4052,7 +4044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF47E0B1-2CBF-4292-BC82-2B6B8F874BC3}">
-  <dimension ref="A1:B1254"/>
+  <dimension ref="A1:B1366"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -14087,8 +14079,904 @@
         <v>1213</v>
       </c>
     </row>
+    <row r="1255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1255" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1256" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1257" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1258" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1259" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1260" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1261" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1262" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1263" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1264" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1265" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1266" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1267" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1268" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1269" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1270" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1271" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1272" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1273" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1274" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1275" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1276" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1277" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1278" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1279" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1280" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1281" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1282" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1283" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1284" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1285" t="s">
+        <v>511</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1286" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1287" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1288" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1289" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1290" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1291" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1292" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1293" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1294" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1295" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1296" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1297" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1298" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1299" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1300" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1301" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1302" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1303" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1304" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1305" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1306" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1307" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1308" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1309" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1310" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1311" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1312" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1313" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1314" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1315" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1316" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1317" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1318" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1319" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1320" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1321" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1322" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1323" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1324" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1325" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1326" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1327" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1328" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1329" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1330" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1331" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1332" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1333" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1334" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1335" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1336" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1337" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1338" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1339" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1340" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1341" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1342" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1343" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1344" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1345" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1346" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1347" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1348" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1349" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1350" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1351" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1352" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1353" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1354" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1355" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1356" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1357" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1358" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1359" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1360" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1361" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1362" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1363" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1364" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1365" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1366" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1214</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1254" xr:uid="{EF47E0B1-2CBF-4292-BC82-2B6B8F874BC3}"/>
+  <autoFilter ref="A1:B1366" xr:uid="{EF47E0B1-2CBF-4292-BC82-2B6B8F874BC3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>